--- a/artfynd/A 16941-2023 artfynd.xlsx
+++ b/artfynd/A 16941-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 16941-2023 artfynd.xlsx
+++ b/artfynd/A 16941-2023 artfynd.xlsx
@@ -1177,7 +1177,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117538611</v>
+        <v>117538624</v>
       </c>
       <c r="B6" t="n">
         <v>97836</v>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>434000</v>
+        <v>434274</v>
       </c>
       <c r="R6" t="n">
-        <v>6380750</v>
+        <v>6380489</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1292,7 +1292,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117538612</v>
+        <v>117538618</v>
       </c>
       <c r="B7" t="n">
         <v>97836</v>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1344,10 +1344,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>433974</v>
+        <v>433965</v>
       </c>
       <c r="R7" t="n">
-        <v>6380733</v>
+        <v>6380667</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1407,7 +1407,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117538618</v>
+        <v>117538634</v>
       </c>
       <c r="B8" t="n">
         <v>97836</v>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>433965</v>
+        <v>434059</v>
       </c>
       <c r="R8" t="n">
-        <v>6380667</v>
+        <v>6380454</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1522,7 +1522,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117538615</v>
+        <v>117538611</v>
       </c>
       <c r="B9" t="n">
         <v>97836</v>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>433946</v>
+        <v>434000</v>
       </c>
       <c r="R9" t="n">
-        <v>6380669</v>
+        <v>6380750</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1637,7 +1637,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117538634</v>
+        <v>117538616</v>
       </c>
       <c r="B10" t="n">
         <v>97836</v>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>434059</v>
+        <v>433950</v>
       </c>
       <c r="R10" t="n">
-        <v>6380454</v>
+        <v>6380669</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1719,12 +1719,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1752,7 +1752,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117538633</v>
+        <v>117538613</v>
       </c>
       <c r="B11" t="n">
         <v>97836</v>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>433983</v>
+        <v>433968</v>
       </c>
       <c r="R11" t="n">
-        <v>6380372</v>
+        <v>6380728</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1867,7 +1867,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117538617</v>
+        <v>117538619</v>
       </c>
       <c r="B12" t="n">
         <v>97836</v>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>433954</v>
+        <v>434000</v>
       </c>
       <c r="R12" t="n">
-        <v>6380668</v>
+        <v>6380444</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1982,7 +1982,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117538613</v>
+        <v>117538633</v>
       </c>
       <c r="B13" t="n">
         <v>97836</v>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2034,10 +2034,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>433968</v>
+        <v>433983</v>
       </c>
       <c r="R13" t="n">
-        <v>6380728</v>
+        <v>6380372</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2064,12 +2064,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2097,7 +2097,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117538619</v>
+        <v>117538617</v>
       </c>
       <c r="B14" t="n">
         <v>97836</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2149,10 +2149,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>434000</v>
+        <v>433954</v>
       </c>
       <c r="R14" t="n">
-        <v>6380444</v>
+        <v>6380668</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2212,7 +2212,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117538625</v>
+        <v>117538615</v>
       </c>
       <c r="B15" t="n">
         <v>97836</v>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>433986</v>
+        <v>433946</v>
       </c>
       <c r="R15" t="n">
-        <v>6380453</v>
+        <v>6380669</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2294,12 +2294,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2442,7 +2442,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117538624</v>
+        <v>117538625</v>
       </c>
       <c r="B17" t="n">
         <v>97836</v>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>434274</v>
+        <v>433986</v>
       </c>
       <c r="R17" t="n">
-        <v>6380489</v>
+        <v>6380453</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2557,7 +2557,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117538616</v>
+        <v>117538612</v>
       </c>
       <c r="B18" t="n">
         <v>97836</v>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2609,10 +2609,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>433950</v>
+        <v>433974</v>
       </c>
       <c r="R18" t="n">
-        <v>6380669</v>
+        <v>6380733</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>

--- a/artfynd/A 16941-2023 artfynd.xlsx
+++ b/artfynd/A 16941-2023 artfynd.xlsx
@@ -1177,10 +1177,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117538624</v>
+        <v>117538619</v>
       </c>
       <c r="B6" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>434274</v>
+        <v>434000</v>
       </c>
       <c r="R6" t="n">
-        <v>6380489</v>
+        <v>6380444</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1292,10 +1292,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117538618</v>
+        <v>117538624</v>
       </c>
       <c r="B7" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1344,10 +1344,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>433965</v>
+        <v>434274</v>
       </c>
       <c r="R7" t="n">
-        <v>6380667</v>
+        <v>6380489</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1374,12 +1374,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1407,10 +1407,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117538634</v>
+        <v>117538612</v>
       </c>
       <c r="B8" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>434059</v>
+        <v>433974</v>
       </c>
       <c r="R8" t="n">
-        <v>6380454</v>
+        <v>6380733</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1525,7 +1525,7 @@
         <v>117538611</v>
       </c>
       <c r="B9" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1637,10 +1637,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117538616</v>
+        <v>117538625</v>
       </c>
       <c r="B10" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>433950</v>
+        <v>433986</v>
       </c>
       <c r="R10" t="n">
-        <v>6380669</v>
+        <v>6380453</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1719,12 +1719,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1752,10 +1752,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117538613</v>
+        <v>117538618</v>
       </c>
       <c r="B11" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>433968</v>
+        <v>433965</v>
       </c>
       <c r="R11" t="n">
-        <v>6380728</v>
+        <v>6380667</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1867,10 +1867,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117538619</v>
+        <v>117538613</v>
       </c>
       <c r="B12" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>434000</v>
+        <v>433968</v>
       </c>
       <c r="R12" t="n">
-        <v>6380444</v>
+        <v>6380728</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1985,7 +1985,7 @@
         <v>117538633</v>
       </c>
       <c r="B13" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2097,10 +2097,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117538617</v>
+        <v>117538614</v>
       </c>
       <c r="B14" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2149,10 +2149,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>433954</v>
+        <v>433964</v>
       </c>
       <c r="R14" t="n">
-        <v>6380668</v>
+        <v>6380690</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2212,10 +2212,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117538615</v>
+        <v>117538617</v>
       </c>
       <c r="B15" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>433946</v>
+        <v>433954</v>
       </c>
       <c r="R15" t="n">
-        <v>6380669</v>
+        <v>6380668</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2327,10 +2327,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117538614</v>
+        <v>117538615</v>
       </c>
       <c r="B16" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>433964</v>
+        <v>433946</v>
       </c>
       <c r="R16" t="n">
-        <v>6380690</v>
+        <v>6380669</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2442,10 +2442,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117538625</v>
+        <v>117538634</v>
       </c>
       <c r="B17" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>433986</v>
+        <v>434059</v>
       </c>
       <c r="R17" t="n">
-        <v>6380453</v>
+        <v>6380454</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2557,10 +2557,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117538612</v>
+        <v>117538616</v>
       </c>
       <c r="B18" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2609,10 +2609,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>433974</v>
+        <v>433950</v>
       </c>
       <c r="R18" t="n">
-        <v>6380733</v>
+        <v>6380669</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>

--- a/artfynd/A 16941-2023 artfynd.xlsx
+++ b/artfynd/A 16941-2023 artfynd.xlsx
@@ -2672,10 +2672,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119861534</v>
+        <v>119861539</v>
       </c>
       <c r="B19" t="n">
-        <v>74577</v>
+        <v>4772</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2688,26 +2688,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6426</v>
+        <v>102306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2884,10 +2886,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119861539</v>
+        <v>119861534</v>
       </c>
       <c r="B21" t="n">
-        <v>4772</v>
+        <v>74577</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2900,28 +2902,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102306</v>
+        <v>6426</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>

--- a/artfynd/A 16941-2023 artfynd.xlsx
+++ b/artfynd/A 16941-2023 artfynd.xlsx
@@ -2672,10 +2672,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119861539</v>
+        <v>119861784</v>
       </c>
       <c r="B19" t="n">
-        <v>4772</v>
+        <v>97928</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2688,28 +2688,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102306</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2717,10 +2716,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>434151</v>
+        <v>434200</v>
       </c>
       <c r="R19" t="n">
-        <v>6380419</v>
+        <v>6380440</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2780,10 +2779,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119861514</v>
+        <v>119861539</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
+        <v>4772</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2792,30 +2791,32 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>102306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2823,10 +2824,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434157</v>
+        <v>434151</v>
       </c>
       <c r="R20" t="n">
-        <v>6380386</v>
+        <v>6380419</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2886,10 +2887,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119861534</v>
+        <v>119861514</v>
       </c>
       <c r="B21" t="n">
-        <v>74577</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2898,25 +2899,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2929,10 +2930,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>434151</v>
+        <v>434157</v>
       </c>
       <c r="R21" t="n">
-        <v>6380419</v>
+        <v>6380386</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2992,10 +2993,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119861784</v>
+        <v>119861534</v>
       </c>
       <c r="B22" t="n">
-        <v>97928</v>
+        <v>74577</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3008,27 +3009,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>6426</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3036,10 +3036,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>434200</v>
+        <v>434151</v>
       </c>
       <c r="R22" t="n">
-        <v>6380440</v>
+        <v>6380419</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 16941-2023 artfynd.xlsx
+++ b/artfynd/A 16941-2023 artfynd.xlsx
@@ -2672,10 +2672,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119861784</v>
+        <v>119861539</v>
       </c>
       <c r="B19" t="n">
-        <v>97928</v>
+        <v>4772</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2688,27 +2688,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>102306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2716,10 +2717,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>434200</v>
+        <v>434151</v>
       </c>
       <c r="R19" t="n">
-        <v>6380440</v>
+        <v>6380419</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2779,10 +2780,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119861539</v>
+        <v>119861784</v>
       </c>
       <c r="B20" t="n">
-        <v>4772</v>
+        <v>97928</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2795,28 +2796,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102306</v>
+        <v>221952</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434151</v>
+        <v>434200</v>
       </c>
       <c r="R20" t="n">
-        <v>6380419</v>
+        <v>6380440</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2887,10 +2887,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119861514</v>
+        <v>119861534</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>74577</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2899,25 +2899,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2930,10 +2930,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>434157</v>
+        <v>434151</v>
       </c>
       <c r="R21" t="n">
-        <v>6380386</v>
+        <v>6380419</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2993,10 +2993,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119861534</v>
+        <v>119861514</v>
       </c>
       <c r="B22" t="n">
-        <v>74577</v>
+        <v>78526</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3005,25 +3005,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3036,10 +3036,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>434151</v>
+        <v>434157</v>
       </c>
       <c r="R22" t="n">
-        <v>6380419</v>
+        <v>6380386</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 16941-2023 artfynd.xlsx
+++ b/artfynd/A 16941-2023 artfynd.xlsx
@@ -2672,10 +2672,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119861539</v>
+        <v>119861514</v>
       </c>
       <c r="B19" t="n">
-        <v>4772</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2684,32 +2684,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102306</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2717,10 +2715,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>434151</v>
+        <v>434157</v>
       </c>
       <c r="R19" t="n">
-        <v>6380419</v>
+        <v>6380386</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2780,10 +2778,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119861784</v>
+        <v>119861534</v>
       </c>
       <c r="B20" t="n">
-        <v>97928</v>
+        <v>74593</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2796,27 +2794,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221952</v>
+        <v>6426</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2824,10 +2821,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434200</v>
+        <v>434151</v>
       </c>
       <c r="R20" t="n">
-        <v>6380440</v>
+        <v>6380419</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2887,10 +2884,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119861534</v>
+        <v>119861784</v>
       </c>
       <c r="B21" t="n">
-        <v>74577</v>
+        <v>97951</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2903,26 +2900,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6426</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2930,10 +2928,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>434151</v>
+        <v>434200</v>
       </c>
       <c r="R21" t="n">
-        <v>6380419</v>
+        <v>6380440</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2993,10 +2991,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119861514</v>
+        <v>119861539</v>
       </c>
       <c r="B22" t="n">
-        <v>78526</v>
+        <v>4772</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3005,30 +3003,32 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>102306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3036,10 +3036,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>434157</v>
+        <v>434151</v>
       </c>
       <c r="R22" t="n">
-        <v>6380386</v>
+        <v>6380419</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 16941-2023 artfynd.xlsx
+++ b/artfynd/A 16941-2023 artfynd.xlsx
@@ -2672,10 +2672,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119861514</v>
+        <v>119861784</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>97951</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2684,30 +2684,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2715,10 +2716,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>434157</v>
+        <v>434200</v>
       </c>
       <c r="R19" t="n">
-        <v>6380386</v>
+        <v>6380440</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2884,10 +2885,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119861784</v>
+        <v>119861514</v>
       </c>
       <c r="B21" t="n">
-        <v>97951</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2896,31 +2897,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2928,10 +2928,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>434200</v>
+        <v>434157</v>
       </c>
       <c r="R21" t="n">
-        <v>6380440</v>
+        <v>6380386</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 16941-2023 artfynd.xlsx
+++ b/artfynd/A 16941-2023 artfynd.xlsx
@@ -2672,10 +2672,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119861784</v>
+        <v>119861539</v>
       </c>
       <c r="B19" t="n">
-        <v>97951</v>
+        <v>4772</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2688,27 +2688,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>102306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2716,10 +2717,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>434200</v>
+        <v>434151</v>
       </c>
       <c r="R19" t="n">
-        <v>6380440</v>
+        <v>6380419</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2779,10 +2780,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119861534</v>
+        <v>119861514</v>
       </c>
       <c r="B20" t="n">
-        <v>74593</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2791,25 +2792,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2822,10 +2823,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434151</v>
+        <v>434157</v>
       </c>
       <c r="R20" t="n">
-        <v>6380419</v>
+        <v>6380386</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2885,10 +2886,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119861514</v>
+        <v>119861784</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>97951</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2897,30 +2898,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2928,10 +2930,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>434157</v>
+        <v>434200</v>
       </c>
       <c r="R21" t="n">
-        <v>6380386</v>
+        <v>6380440</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2991,10 +2993,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119861539</v>
+        <v>119861534</v>
       </c>
       <c r="B22" t="n">
-        <v>4772</v>
+        <v>74593</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3007,28 +3009,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102306</v>
+        <v>6426</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>

--- a/artfynd/A 16941-2023 artfynd.xlsx
+++ b/artfynd/A 16941-2023 artfynd.xlsx
@@ -2672,10 +2672,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119861539</v>
+        <v>119861784</v>
       </c>
       <c r="B19" t="n">
-        <v>4772</v>
+        <v>97951</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2688,28 +2688,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102306</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2717,10 +2716,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>434151</v>
+        <v>434200</v>
       </c>
       <c r="R19" t="n">
-        <v>6380419</v>
+        <v>6380440</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2886,10 +2885,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119861784</v>
+        <v>119861539</v>
       </c>
       <c r="B21" t="n">
-        <v>97951</v>
+        <v>4772</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2902,27 +2901,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>102306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2930,10 +2930,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>434200</v>
+        <v>434151</v>
       </c>
       <c r="R21" t="n">
-        <v>6380440</v>
+        <v>6380419</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 16941-2023 artfynd.xlsx
+++ b/artfynd/A 16941-2023 artfynd.xlsx
@@ -2672,10 +2672,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119861784</v>
+        <v>119861539</v>
       </c>
       <c r="B19" t="n">
-        <v>97951</v>
+        <v>4772</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2688,27 +2688,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>102306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2716,10 +2717,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>434200</v>
+        <v>434151</v>
       </c>
       <c r="R19" t="n">
-        <v>6380440</v>
+        <v>6380419</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2885,10 +2886,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119861539</v>
+        <v>119861534</v>
       </c>
       <c r="B21" t="n">
-        <v>4772</v>
+        <v>74593</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2901,28 +2902,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102306</v>
+        <v>6426</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2993,10 +2992,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119861534</v>
+        <v>119861784</v>
       </c>
       <c r="B22" t="n">
-        <v>74593</v>
+        <v>97951</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3009,26 +3008,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6426</v>
+        <v>221952</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3036,10 +3036,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>434151</v>
+        <v>434200</v>
       </c>
       <c r="R22" t="n">
-        <v>6380419</v>
+        <v>6380440</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 16941-2023 artfynd.xlsx
+++ b/artfynd/A 16941-2023 artfynd.xlsx
@@ -802,12 +802,7 @@
         <v>74469766</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -839,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>434064.5372402068</v>
+        <v>434065</v>
       </c>
       <c r="R3" t="n">
-        <v>6380458.609336157</v>
+        <v>6380459</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -872,19 +867,9 @@
           <t>1983-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1987-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -928,12 +913,7 @@
         <v>74604554</v>
       </c>
       <c r="B4" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97465</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -965,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>434064.5372402068</v>
+        <v>434065</v>
       </c>
       <c r="R4" t="n">
-        <v>6380458.609336157</v>
+        <v>6380459</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -998,19 +978,9 @@
           <t>1983-01-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1987-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1054,12 +1024,7 @@
         <v>74857211</v>
       </c>
       <c r="B5" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105642</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>434064.5372402068</v>
+        <v>434065</v>
       </c>
       <c r="R5" t="n">
-        <v>6380458.609336157</v>
+        <v>6380459</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1124,19 +1089,9 @@
           <t>1983-01-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1987-12-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">

--- a/artfynd/A 16941-2023 artfynd.xlsx
+++ b/artfynd/A 16941-2023 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>74469766</v>
       </c>
       <c r="B3" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>74857211</v>
       </c>
       <c r="B5" t="n">
-        <v>105642</v>
+        <v>105651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16941-2023 artfynd.xlsx
+++ b/artfynd/A 16941-2023 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>74469766</v>
       </c>
       <c r="B3" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>74604554</v>
       </c>
       <c r="B4" t="n">
-        <v>97465</v>
+        <v>97466</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>74857211</v>
       </c>
       <c r="B5" t="n">
-        <v>105651</v>
+        <v>105654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16941-2023 artfynd.xlsx
+++ b/artfynd/A 16941-2023 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>74469766</v>
       </c>
       <c r="B3" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>74604554</v>
       </c>
       <c r="B4" t="n">
-        <v>97466</v>
+        <v>97493</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>74857211</v>
       </c>
       <c r="B5" t="n">
-        <v>105654</v>
+        <v>105682</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16941-2023 artfynd.xlsx
+++ b/artfynd/A 16941-2023 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>74469766</v>
       </c>
       <c r="B3" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>74604554</v>
       </c>
       <c r="B4" t="n">
-        <v>97493</v>
+        <v>97499</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>74857211</v>
       </c>
       <c r="B5" t="n">
-        <v>105682</v>
+        <v>105688</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16941-2023 artfynd.xlsx
+++ b/artfynd/A 16941-2023 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>74469766</v>
       </c>
       <c r="B3" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>74604554</v>
       </c>
       <c r="B4" t="n">
-        <v>97499</v>
+        <v>97506</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>74857211</v>
       </c>
       <c r="B5" t="n">
-        <v>105688</v>
+        <v>105695</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16941-2023 artfynd.xlsx
+++ b/artfynd/A 16941-2023 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>74469766</v>
       </c>
       <c r="B3" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>74604554</v>
       </c>
       <c r="B4" t="n">
-        <v>97506</v>
+        <v>97510</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>74857211</v>
       </c>
       <c r="B5" t="n">
-        <v>105695</v>
+        <v>105699</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16941-2023 artfynd.xlsx
+++ b/artfynd/A 16941-2023 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>74469766</v>
       </c>
       <c r="B3" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>74604554</v>
       </c>
       <c r="B4" t="n">
-        <v>97510</v>
+        <v>97517</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>74857211</v>
       </c>
       <c r="B5" t="n">
-        <v>105699</v>
+        <v>105706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16941-2023 artfynd.xlsx
+++ b/artfynd/A 16941-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -802,7 +802,7 @@
         <v>74469766</v>
       </c>
       <c r="B3" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>74604554</v>
       </c>
       <c r="B4" t="n">
-        <v>97520</v>
+        <v>97525</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>74857211</v>
       </c>
       <c r="B5" t="n">
-        <v>105709</v>
+        <v>105714</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3052,6 +3052,220 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129148708</v>
+      </c>
+      <c r="B23" t="n">
+        <v>86951</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1988</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kryddspindling</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Cortinarius percomis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Palsboskogen, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>434028</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6380477</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Vaggeryd</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Bondstorp</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anders Hildingsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anders Hildingsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129148402</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92847</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Palsboskogen, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>434028</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6380477</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Vaggeryd</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Bondstorp</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anders Hildingsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anders Hildingsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16941-2023 artfynd.xlsx
+++ b/artfynd/A 16941-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3057,7 +3057,7 @@
         <v>129148708</v>
       </c>
       <c r="B23" t="n">
-        <v>86951</v>
+        <v>86954</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3083,19 +3083,22 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Palsboskogen, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>434028</v>
+        <v>434027</v>
       </c>
       <c r="R23" t="n">
-        <v>6380477</v>
+        <v>6380494</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3143,6 +3146,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3164,7 +3168,7 @@
         <v>129148402</v>
       </c>
       <c r="B24" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3190,19 +3194,22 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Palsboskogen, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434028</v>
+        <v>434027</v>
       </c>
       <c r="R24" t="n">
-        <v>6380477</v>
+        <v>6380494</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3250,6 +3257,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3265,6 +3273,130 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129159373</v>
+      </c>
+      <c r="B25" t="n">
+        <v>87007</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>3739</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Persiljespindling</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Cortinarius sulfurinus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Palsboskogen, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>434027</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6380494</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Vaggeryd</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Bondstorp</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Stod precis i vägkanten tillsammans med kryddspindling. Svag lukt av dillchips, spormått 11,6 x 6,6, dvs inom men i nedre kanten av artens angivna intervall</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anders Hildingsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anders Hildingsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16941-2023 artfynd.xlsx
+++ b/artfynd/A 16941-2023 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>74469766</v>
       </c>
       <c r="B3" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>74604554</v>
       </c>
       <c r="B4" t="n">
-        <v>97525</v>
+        <v>97533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>74857211</v>
       </c>
       <c r="B5" t="n">
-        <v>105714</v>
+        <v>105722</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>129148708</v>
       </c>
       <c r="B23" t="n">
-        <v>86954</v>
+        <v>86957</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3165,36 +3165,44 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129148402</v>
+        <v>129159373</v>
       </c>
       <c r="B24" t="n">
-        <v>92852</v>
+        <v>87010</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>3739</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -3238,7 +3246,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3248,7 +3256,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Stod precis i vägkanten tillsammans med kryddspindling. Svag lukt av dillchips, spormått 11,6 x 6,6, dvs inom men i nedre kanten av artens angivna intervall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3276,44 +3289,36 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129159373</v>
+        <v>129148402</v>
       </c>
       <c r="B25" t="n">
-        <v>87007</v>
+        <v>92855</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3739</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Quél.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3357,7 +3362,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3367,12 +3372,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Stod precis i vägkanten tillsammans med kryddspindling. Svag lukt av dillchips, spormått 11,6 x 6,6, dvs inom men i nedre kanten av artens angivna intervall</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 16941-2023 artfynd.xlsx
+++ b/artfynd/A 16941-2023 artfynd.xlsx
@@ -3165,44 +3165,36 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129159373</v>
+        <v>129148402</v>
       </c>
       <c r="B24" t="n">
-        <v>87010</v>
+        <v>92855</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3739</v>
+        <v>5964</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Quél.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -3246,7 +3238,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3256,12 +3248,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Stod precis i vägkanten tillsammans med kryddspindling. Svag lukt av dillchips, spormått 11,6 x 6,6, dvs inom men i nedre kanten av artens angivna intervall</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3289,36 +3276,44 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129148402</v>
+        <v>129159373</v>
       </c>
       <c r="B25" t="n">
-        <v>92855</v>
+        <v>87010</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5964</v>
+        <v>3739</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3362,7 +3357,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3372,7 +3367,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Stod precis i vägkanten tillsammans med kryddspindling. Svag lukt av dillchips, spormått 11,6 x 6,6, dvs inom men i nedre kanten av artens angivna intervall</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 16941-2023 artfynd.xlsx
+++ b/artfynd/A 16941-2023 artfynd.xlsx
@@ -3165,36 +3165,44 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129148402</v>
+        <v>129159373</v>
       </c>
       <c r="B24" t="n">
-        <v>92855</v>
+        <v>87010</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>3739</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -3238,7 +3246,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3248,7 +3256,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Stod precis i vägkanten tillsammans med kryddspindling. Svag lukt av dillchips, spormått 11,6 x 6,6, dvs inom men i nedre kanten av artens angivna intervall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3276,44 +3289,36 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129159373</v>
+        <v>129148402</v>
       </c>
       <c r="B25" t="n">
-        <v>87010</v>
+        <v>92855</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3739</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Quél.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3357,7 +3362,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3367,12 +3372,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Stod precis i vägkanten tillsammans med kryddspindling. Svag lukt av dillchips, spormått 11,6 x 6,6, dvs inom men i nedre kanten av artens angivna intervall</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 16941-2023 artfynd.xlsx
+++ b/artfynd/A 16941-2023 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>74469766</v>
       </c>
       <c r="B3" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>74604554</v>
       </c>
       <c r="B4" t="n">
-        <v>97533</v>
+        <v>97543</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>74857211</v>
       </c>
       <c r="B5" t="n">
-        <v>105722</v>
+        <v>105732</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>129148708</v>
       </c>
       <c r="B23" t="n">
-        <v>86957</v>
+        <v>86961</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3165,44 +3165,36 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129159373</v>
+        <v>129148402</v>
       </c>
       <c r="B24" t="n">
-        <v>87010</v>
+        <v>92862</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3739</v>
+        <v>5964</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Quél.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -3246,7 +3238,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3256,12 +3248,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Stod precis i vägkanten tillsammans med kryddspindling. Svag lukt av dillchips, spormått 11,6 x 6,6, dvs inom men i nedre kanten av artens angivna intervall</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3289,36 +3276,44 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129148402</v>
+        <v>129159373</v>
       </c>
       <c r="B25" t="n">
-        <v>92855</v>
+        <v>87014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5964</v>
+        <v>3739</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3362,7 +3357,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3372,7 +3367,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Stod precis i vägkanten tillsammans med kryddspindling. Svag lukt av dillchips, spormått 11,6 x 6,6, dvs inom men i nedre kanten av artens angivna intervall</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 16941-2023 artfynd.xlsx
+++ b/artfynd/A 16941-2023 artfynd.xlsx
@@ -3057,7 +3057,7 @@
         <v>129148708</v>
       </c>
       <c r="B23" t="n">
-        <v>86961</v>
+        <v>86968</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>129148402</v>
       </c>
       <c r="B24" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>129159373</v>
       </c>
       <c r="B25" t="n">
-        <v>87014</v>
+        <v>87021</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 16941-2023 artfynd.xlsx
+++ b/artfynd/A 16941-2023 artfynd.xlsx
@@ -3057,7 +3057,7 @@
         <v>129148708</v>
       </c>
       <c r="B23" t="n">
-        <v>86968</v>
+        <v>86970</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3165,36 +3165,44 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129148402</v>
+        <v>129159373</v>
       </c>
       <c r="B24" t="n">
-        <v>92869</v>
+        <v>87023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>3739</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -3238,7 +3246,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3248,7 +3256,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Stod precis i vägkanten tillsammans med kryddspindling. Svag lukt av dillchips, spormått 11,6 x 6,6, dvs inom men i nedre kanten av artens angivna intervall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3276,44 +3289,36 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129159373</v>
+        <v>129148402</v>
       </c>
       <c r="B25" t="n">
-        <v>87021</v>
+        <v>92871</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3739</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Quél.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3357,7 +3362,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3367,12 +3372,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Stod precis i vägkanten tillsammans med kryddspindling. Svag lukt av dillchips, spormått 11,6 x 6,6, dvs inom men i nedre kanten av artens angivna intervall</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 16941-2023 artfynd.xlsx
+++ b/artfynd/A 16941-2023 artfynd.xlsx
@@ -3057,7 +3057,7 @@
         <v>129148708</v>
       </c>
       <c r="B23" t="n">
-        <v>86970</v>
+        <v>86971</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3165,44 +3165,36 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129159373</v>
+        <v>129148402</v>
       </c>
       <c r="B24" t="n">
-        <v>87023</v>
+        <v>92857</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3739</v>
+        <v>5964</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Quél.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -3246,7 +3238,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3256,12 +3248,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Stod precis i vägkanten tillsammans med kryddspindling. Svag lukt av dillchips, spormått 11,6 x 6,6, dvs inom men i nedre kanten av artens angivna intervall</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3289,36 +3276,44 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129148402</v>
+        <v>129159373</v>
       </c>
       <c r="B25" t="n">
-        <v>92871</v>
+        <v>87024</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5964</v>
+        <v>3739</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3362,7 +3357,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3372,7 +3367,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Stod precis i vägkanten tillsammans med kryddspindling. Svag lukt av dillchips, spormått 11,6 x 6,6, dvs inom men i nedre kanten av artens angivna intervall</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 16941-2023 artfynd.xlsx
+++ b/artfynd/A 16941-2023 artfynd.xlsx
@@ -3168,7 +3168,7 @@
         <v>129148402</v>
       </c>
       <c r="B24" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 16941-2023 artfynd.xlsx
+++ b/artfynd/A 16941-2023 artfynd.xlsx
@@ -3165,36 +3165,44 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129148402</v>
+        <v>129159373</v>
       </c>
       <c r="B24" t="n">
-        <v>92858</v>
+        <v>87024</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>3739</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -3238,7 +3246,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3248,7 +3256,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Stod precis i vägkanten tillsammans med kryddspindling. Svag lukt av dillchips, spormått 11,6 x 6,6, dvs inom men i nedre kanten av artens angivna intervall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3276,44 +3289,36 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129159373</v>
+        <v>129148402</v>
       </c>
       <c r="B25" t="n">
-        <v>87024</v>
+        <v>92858</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3739</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Quél.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3357,7 +3362,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3367,12 +3372,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Stod precis i vägkanten tillsammans med kryddspindling. Svag lukt av dillchips, spormått 11,6 x 6,6, dvs inom men i nedre kanten av artens angivna intervall</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 16941-2023 artfynd.xlsx
+++ b/artfynd/A 16941-2023 artfynd.xlsx
@@ -3057,7 +3057,7 @@
         <v>129148708</v>
       </c>
       <c r="B23" t="n">
-        <v>86971</v>
+        <v>86974</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3165,44 +3165,36 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129159373</v>
+        <v>129148402</v>
       </c>
       <c r="B24" t="n">
-        <v>87024</v>
+        <v>92861</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3739</v>
+        <v>5964</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Quél.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -3246,7 +3238,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3256,12 +3248,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Stod precis i vägkanten tillsammans med kryddspindling. Svag lukt av dillchips, spormått 11,6 x 6,6, dvs inom men i nedre kanten av artens angivna intervall</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3289,36 +3276,44 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129148402</v>
+        <v>129159373</v>
       </c>
       <c r="B25" t="n">
-        <v>92858</v>
+        <v>87027</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5964</v>
+        <v>3739</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3362,7 +3357,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3372,7 +3367,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Stod precis i vägkanten tillsammans med kryddspindling. Svag lukt av dillchips, spormått 11,6 x 6,6, dvs inom men i nedre kanten av artens angivna intervall</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 16941-2023 artfynd.xlsx
+++ b/artfynd/A 16941-2023 artfynd.xlsx
@@ -3057,7 +3057,7 @@
         <v>129148708</v>
       </c>
       <c r="B23" t="n">
-        <v>86974</v>
+        <v>86976</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>129148402</v>
       </c>
       <c r="B24" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>129159373</v>
       </c>
       <c r="B25" t="n">
-        <v>87027</v>
+        <v>87029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 16941-2023 artfynd.xlsx
+++ b/artfynd/A 16941-2023 artfynd.xlsx
@@ -3057,7 +3057,7 @@
         <v>129148708</v>
       </c>
       <c r="B23" t="n">
-        <v>86976</v>
+        <v>86980</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3165,36 +3165,44 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129148402</v>
+        <v>129159373</v>
       </c>
       <c r="B24" t="n">
-        <v>92863</v>
+        <v>87033</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>3739</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -3238,7 +3246,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3248,7 +3256,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Stod precis i vägkanten tillsammans med kryddspindling. Svag lukt av dillchips, spormått 11,6 x 6,6, dvs inom men i nedre kanten av artens angivna intervall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3276,44 +3289,36 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129159373</v>
+        <v>129148402</v>
       </c>
       <c r="B25" t="n">
-        <v>87029</v>
+        <v>92867</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3739</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Quél.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3357,7 +3362,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3367,12 +3372,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Stod precis i vägkanten tillsammans med kryddspindling. Svag lukt av dillchips, spormått 11,6 x 6,6, dvs inom men i nedre kanten av artens angivna intervall</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 16941-2023 artfynd.xlsx
+++ b/artfynd/A 16941-2023 artfynd.xlsx
@@ -3057,7 +3057,7 @@
         <v>129148708</v>
       </c>
       <c r="B23" t="n">
-        <v>86980</v>
+        <v>86981</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>129159373</v>
       </c>
       <c r="B24" t="n">
-        <v>87033</v>
+        <v>87034</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>129148402</v>
       </c>
       <c r="B25" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 16941-2023 artfynd.xlsx
+++ b/artfynd/A 16941-2023 artfynd.xlsx
@@ -3165,44 +3165,36 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129159373</v>
+        <v>129148402</v>
       </c>
       <c r="B24" t="n">
-        <v>87034</v>
+        <v>92871</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3739</v>
+        <v>5964</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Quél.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -3246,7 +3238,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3256,12 +3248,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Stod precis i vägkanten tillsammans med kryddspindling. Svag lukt av dillchips, spormått 11,6 x 6,6, dvs inom men i nedre kanten av artens angivna intervall</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3289,36 +3276,44 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129148402</v>
+        <v>129159373</v>
       </c>
       <c r="B25" t="n">
-        <v>92868</v>
+        <v>87034</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5964</v>
+        <v>3739</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3362,7 +3357,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3372,7 +3367,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Stod precis i vägkanten tillsammans med kryddspindling. Svag lukt av dillchips, spormått 11,6 x 6,6, dvs inom men i nedre kanten av artens angivna intervall</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 16941-2023 artfynd.xlsx
+++ b/artfynd/A 16941-2023 artfynd.xlsx
@@ -3165,36 +3165,44 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129148402</v>
+        <v>129159373</v>
       </c>
       <c r="B24" t="n">
-        <v>92871</v>
+        <v>87034</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>3739</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -3238,7 +3246,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3248,7 +3256,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Stod precis i vägkanten tillsammans med kryddspindling. Svag lukt av dillchips, spormått 11,6 x 6,6, dvs inom men i nedre kanten av artens angivna intervall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3276,44 +3289,36 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129159373</v>
+        <v>129148402</v>
       </c>
       <c r="B25" t="n">
-        <v>87034</v>
+        <v>92871</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3739</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Quél.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3357,7 +3362,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3367,12 +3372,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Stod precis i vägkanten tillsammans med kryddspindling. Svag lukt av dillchips, spormått 11,6 x 6,6, dvs inom men i nedre kanten av artens angivna intervall</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 16941-2023 artfynd.xlsx
+++ b/artfynd/A 16941-2023 artfynd.xlsx
@@ -3165,44 +3165,36 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129159373</v>
+        <v>129148402</v>
       </c>
       <c r="B24" t="n">
-        <v>87034</v>
+        <v>92871</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3739</v>
+        <v>5964</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Quél.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -3246,7 +3238,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3256,12 +3248,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Stod precis i vägkanten tillsammans med kryddspindling. Svag lukt av dillchips, spormått 11,6 x 6,6, dvs inom men i nedre kanten av artens angivna intervall</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3289,36 +3276,44 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129148402</v>
+        <v>129159373</v>
       </c>
       <c r="B25" t="n">
-        <v>92871</v>
+        <v>87034</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5964</v>
+        <v>3739</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3362,7 +3357,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3372,7 +3367,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Stod precis i vägkanten tillsammans med kryddspindling. Svag lukt av dillchips, spormått 11,6 x 6,6, dvs inom men i nedre kanten av artens angivna intervall</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 16941-2023 artfynd.xlsx
+++ b/artfynd/A 16941-2023 artfynd.xlsx
@@ -3057,7 +3057,7 @@
         <v>129148708</v>
       </c>
       <c r="B23" t="n">
-        <v>86981</v>
+        <v>87009</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3165,36 +3165,44 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129148402</v>
+        <v>129159373</v>
       </c>
       <c r="B24" t="n">
-        <v>92871</v>
+        <v>87062</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>3739</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -3238,7 +3246,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3248,7 +3256,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Stod precis i vägkanten tillsammans med kryddspindling. Svag lukt av dillchips, spormått 11,6 x 6,6, dvs inom men i nedre kanten av artens angivna intervall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3276,44 +3289,36 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129159373</v>
+        <v>129148402</v>
       </c>
       <c r="B25" t="n">
-        <v>87034</v>
+        <v>92899</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3739</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Quél.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3357,7 +3362,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3367,12 +3372,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Stod precis i vägkanten tillsammans med kryddspindling. Svag lukt av dillchips, spormått 11,6 x 6,6, dvs inom men i nedre kanten av artens angivna intervall</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 16941-2023 artfynd.xlsx
+++ b/artfynd/A 16941-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,8 +788,16 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128294908</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>